--- a/public/documents/pieces-reponse-1/R1-abattements-double-emploi.xlsx
+++ b/public/documents/pieces-reponse-1/R1-abattements-double-emploi.xlsx
@@ -692,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -717,7 +717,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Perimetre : hors cuisine et hors alcool des menus. Litres : mesures par exercice quand la source le permet, sinon repartis selon la cle indiquee. Euros : prix de revente au litre issus de nos propres donnees (src/data/boissonsPageData.json), sauf consommation du chef et offerts, repris du fichier 56 remis au service.</t>
+          <t>Perimetre : hors cuisine et hors alcool des menus. Litres : mesures par exercice quand la source le permet, sinon repartis selon la cle indiquee. Euros : prix de revente au litre issus de nos propres donnees, sauf consommation du chef et offerts, repris du fichier 56 remis au service. Volumes et euros lus dans src/data/reponse1Calculs/cascade-10622.json, source unique de la cascade. Les offerts deja enregistres a 0,00 EUR (25,75 L) sont deja compris dans les postes de vente de la cascade : ils ne sont pas reclames une seconde fois ici.</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Consommation du chef (Picon + Macvin)</t>
+          <t>Consommation du chef (Picon et macvin)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
@@ -805,50 +805,50 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>litres mesures par exercice ; valorisation du fichier 56 (Macvin + Picon)</t>
+          <t>valorisation du fichier 56 remis au service</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Aperitifs offerts aux clients</t>
+          <t>Offerts non enregistrés en caisse</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>13.3</v>
+        <v>4.7</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>13.3</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>39.7</v>
+        <v>14</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1222</v>
+        <v>430</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1222</v>
+        <v>430</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1197</v>
+        <v>421</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>3641</v>
+        <v>1281</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>base journaliere (1 aperitif 6 cl/jour x 662 j), prorata jours de service</t>
+          <t>91.71 €/L (prix de revente d’un apéritif)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Cafes offerts (hors volume d'alcool)</t>
+          <t>Cafés offerts (sans volume d’alcool)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
@@ -864,232 +864,196 @@
         <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1467</v>
+        <v>1456</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1467</v>
+        <v>1456</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1436</v>
+        <v>1456</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>4369</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>base journaliere (3 cafes/jour x 662 j), prorata jours de service</t>
+          <t>3 cafés par jour x 662 jours, fichier 56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Sur-versement (vins, spiritueux, cocktails)</t>
+          <t>Sur-versement au verre</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>247.7</v>
+        <v>163.5</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>236.7</v>
+        <v>166.1</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>236.1</v>
+        <v>164.3</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>720.5</v>
+        <v>493.9</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>18579</v>
+        <v>14278</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>17754</v>
+        <v>14508</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>17709</v>
+        <v>14349</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>54041</v>
+        <v>43135</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>litres mesures par exercice ; 75.01 €/L (moyenne ponderee des regimes servis)</t>
+          <t>87.33 €/L (moyenne pondérée des régimes servis)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Cremant jete en fin de journee</t>
+          <t>Crémant non vendu</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>93.2</v>
+        <v>81.7</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>84.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>82.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>260.2</v>
+        <v>272</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3029</v>
+        <v>2655</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2743</v>
+        <v>3044</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>2684</v>
+        <v>3141</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>8456</v>
+        <v>8841</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>litres mesures par exercice ; 32.50 €/L (prix de revente du cremant)</t>
+          <t>32.50 €/L</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Cremant sur-verse</t>
+          <t>Dégustation offerte</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>25</v>
+        <v>35.4</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>31.7</v>
+        <v>45.1</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>30.3</v>
+        <v>45.3</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>87</v>
+        <v>125.8</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>812</v>
+        <v>1699</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>1030</v>
+        <v>2169</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>986</v>
+        <v>2178</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2828</v>
+        <v>6045</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>prorata du cremant servi ; 32.50 €/L</t>
+          <t>48.04 €/L (prix de revente moyen des vins)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Degustation offerte (note par note)</t>
+          <t>Freinte technique de la bière</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>43.3</v>
+        <v>42.8</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>42</v>
+        <v>38.6</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>40.7</v>
+        <v>39.2</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>126</v>
+        <v>120.5</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>2080</v>
+        <v>667</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>2017</v>
+        <v>602</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1956</v>
+        <v>611</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>6053</v>
+        <v>1880</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>prorata du volume vendu en caisse ; 48.04 €/L (prix de revente des vins)</t>
+          <t>15.60 €/L (fût Affligem)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Freinte technique de la biere pression</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>129</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>713</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>647</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>653</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>2012</v>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>prorata de la freinte mesuree ; 15.60 €/L (fut Affligem)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>TOTAL itemise (hors cuisine et menus)</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
-        <v>516.2</v>
-      </c>
-      <c r="C13" s="7" t="n">
-        <v>497.5</v>
-      </c>
-      <c r="D13" s="7" t="n">
-        <v>491.7</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>1505.4</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>32794</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>31771</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>31411</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>95976</v>
+      <c r="B12" s="7" t="n">
+        <v>376</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>396.2</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>397.1</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>1169.2</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>26078</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>27101</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>26948</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>80126</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="78" customWidth="1" min="1" max="1"/>
@@ -1319,10 +1283,10 @@
         <v>438658.43</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>455249.2</v>
+        <v>435524.92</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>1297938.5</v>
+        <v>1278214.22</v>
       </c>
     </row>
     <row r="15">
@@ -1433,111 +1397,225 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Nos postes itemises, hors cuisine et menus</t>
+          <t>A. Nos postes itemises, hors cuisine et menus</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>1505</v>
+        <v>1169</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>14.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Perte d'exploitation totale, hors cuisine et menus</t>
+          <t>Alcool passe en cuisine et dans les menus, plafonne aux achats factures</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3048</v>
+        <v>745</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>28.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Alcool passe en cuisine (jamais vendu comme boisson)</t>
+          <t>B. Nos postes itemises, cuisine et alcool des menus compris</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>566</v>
+        <v>1914</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Alcool des menus, non detaille en caisse</t>
+          <t>Residu de perte pure (solde du bilan matiere)</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>228</v>
+        <v>2224</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>2.1</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Le forfait de 15 % est deja absorbe par les seuls postes itemises</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>1505</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>94.5</v>
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>C. Perte d'exploitation totale, hors cuisine et menus</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>3393</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>D. Alcool achete et non vendu, cuisine et menus compris</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>4138</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Part du forfait de 15 % que chaque assiette represente, en volume</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>A : 73.4 %</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>B : 120.1 %</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>C : 213.0 %</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>D : 259.7 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Les seuls postes itemises hors cuisine et menus ne suffisent plus a absorber le forfait : ils en representent 73.4 %. C'est l'assiette B, cuisine et alcool des menus compris, qui le depasse la premiere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>C. Comparaison en euros de chiffre d'affaires boissons (3 exercices)</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Euros</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr"/>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Ce que le forfait de 15 % retire au CA boissons reconstitue</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B35" s="6" t="n">
         <v>76863.17999999999</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Nos postes itemises, valorises au prix de revente</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>95975.57000000001</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Ecart</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>19112.39</v>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>A. Nos postes itemises, hors cuisine et menus, valorises au prix de revente</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>80125.89999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ecart de l'assiette A au forfait</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>3262.72</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>B. Cuisine et alcool des menus compris</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>142706.71</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ecart de l'assiette B au forfait</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>65843.53</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>C. Perte d'exploitation totale, hors cuisine et menus</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>166995.35</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ecart de l'assiette C au forfait</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>90132.17</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>D. Alcool achete et non vendu, cuisine et menus compris</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>229576.16</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ecart de l'assiette D au forfait</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>152712.98</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Le residu de perte pure des assiettes C et D est valorise a 39.05 EUR/L, moyenne des prix de revente ponderee par les litres achetes : c'est une moyenne, non une mesure.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/public/documents/pieces-reponse-1/R1-abattements-double-emploi.xlsx
+++ b/public/documents/pieces-reponse-1/R1-abattements-double-emploi.xlsx
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>7</v>
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>1914</v>
+        <v>1910</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>18</v>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>2224</v>
+        <v>2228</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3393</v>
+        <v>3397</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>B : 120.1 %</t>
+          <t>B : 119.9 %</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>C : 213.0 %</t>
+          <t>C : 213.2 %</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>142706.71</v>
+        <v>142254.31</v>
       </c>
     </row>
     <row r="39">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>65843.53</v>
+        <v>65391.13</v>
       </c>
     </row>
     <row r="40">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>166995.35</v>
+        <v>167131.25</v>
       </c>
     </row>
     <row r="41">
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>90132.17</v>
+        <v>90268.07000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>229576.16</v>
+        <v>229259.65</v>
       </c>
     </row>
     <row r="43">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>152712.98</v>
+        <v>152396.47</v>
       </c>
     </row>
     <row r="45">

--- a/public/documents/pieces-reponse-1/R1-abattements-double-emploi.xlsx
+++ b/public/documents/pieces-reponse-1/R1-abattements-double-emploi.xlsx
@@ -888,28 +888,28 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>163.5</v>
+        <v>160.4</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>166.1</v>
+        <v>162.7</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>164.3</v>
+        <v>159.9</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>493.9</v>
+        <v>483</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>14278</v>
+        <v>14010</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>14508</v>
+        <v>14206</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>14349</v>
+        <v>13968</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>43135</v>
+        <v>42184</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -1032,28 +1032,28 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>376</v>
+        <v>372.9</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>396.2</v>
+        <v>392.7</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>397.1</v>
+        <v>392.7</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1169.2</v>
+        <v>1158.4</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>26078</v>
+        <v>25810</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>27101</v>
+        <v>26799</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>26948</v>
+        <v>26566</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>80126</v>
+        <v>79175</v>
       </c>
     </row>
   </sheetData>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>1169</v>
+        <v>1158</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="26">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>1910</v>
+        <v>1899</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="28">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>2228</v>
+        <v>2055</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>21</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="29">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3397</v>
+        <v>3213</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>32</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="30">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>4138</v>
+        <v>3954</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>39</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="31">
@@ -1480,29 +1480,29 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>A : 73.4 %</t>
+          <t>A : 72.7 %</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>B : 119.9 %</t>
+          <t>B : 119.2 %</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>C : 213.2 %</t>
+          <t>C : 201.6 %</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>D : 259.7 %</t>
+          <t>D : 248.2 %</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Les seuls postes itemises hors cuisine et menus ne suffisent plus a absorber le forfait : ils en representent 73.4 %. C'est l'assiette B, cuisine et alcool des menus compris, qui le depasse la premiere.</t>
+          <t>Les seuls postes itemises hors cuisine et menus ne suffisent plus a absorber le forfait : ils en representent 72.7 %. C'est l'assiette B, cuisine et alcool des menus compris, qui le depasse la premiere.</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>80125.89999999999</v>
+        <v>79174.86</v>
       </c>
     </row>
     <row r="37">
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>3262.72</v>
+        <v>2311.68</v>
       </c>
     </row>
     <row r="38">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>142254.31</v>
+        <v>141303.27</v>
       </c>
     </row>
     <row r="39">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>65391.13</v>
+        <v>64440.09</v>
       </c>
     </row>
     <row r="40">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>167131.25</v>
+        <v>159400.83</v>
       </c>
     </row>
     <row r="41">
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>90268.07000000001</v>
+        <v>82537.64999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1598,7 +1598,7 @@
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>229259.65</v>
+        <v>221529.23</v>
       </c>
     </row>
     <row r="43">
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>152396.47</v>
+        <v>144666.05</v>
       </c>
     </row>
     <row r="45">
